--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -7,12 +7,18 @@
   </bookViews>
   <sheets>
     <sheet name="all_Instruments" r:id="rId3" sheetId="1"/>
+    <sheet name="National_TurnOver" r:id="rId4" sheetId="2"/>
+    <sheet name="IndexHeatmap" r:id="rId5" sheetId="3"/>
+    <sheet name="Gain" r:id="rId6" sheetId="4"/>
+    <sheet name="Loss" r:id="rId7" sheetId="5"/>
+    <sheet name="HighLow" r:id="rId8" sheetId="6"/>
+    <sheet name="Above50" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="173">
   <si>
     <t>Types_of_instrument</t>
   </si>
@@ -24,6 +30,515 @@
   </si>
   <si>
     <t>IF</t>
+  </si>
+  <si>
+    <t>Highest Notional Turnover Details</t>
+  </si>
+  <si>
+    <t>Type of Instrument</t>
+  </si>
+  <si>
+    <t>Underlying</t>
+  </si>
+  <si>
+    <t>Expiry Date</t>
+  </si>
+  <si>
+    <t>Strike Price</t>
+  </si>
+  <si>
+    <t>LTP</t>
+  </si>
+  <si>
+    <t>Change %</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Turnover
+(₹ Lac)</t>
+  </si>
+  <si>
+    <t>Notional Turnover
+(₹ Lac)</t>
+  </si>
+  <si>
+    <t>OI</t>
+  </si>
+  <si>
+    <t>SENSEX</t>
+  </si>
+  <si>
+    <t>25 Mar 26</t>
+  </si>
+  <si>
+    <t>75,200</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>-100.00</t>
+  </si>
+  <si>
+    <t>2,73,89,389</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>41,21,63,001.00</t>
+  </si>
+  <si>
+    <t>2,60,988</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>% Change</t>
+  </si>
+  <si>
+    <t>BSE BANKEX</t>
+  </si>
+  <si>
+    <t>60449.02</t>
+  </si>
+  <si>
+    <t>1230.81</t>
+  </si>
+  <si>
+    <t>+2.08%</t>
+  </si>
+  <si>
+    <t>BSE FOCUSED MIDCAP</t>
+  </si>
+  <si>
+    <t>21995.44</t>
+  </si>
+  <si>
+    <t>439.68</t>
+  </si>
+  <si>
+    <t>+2.04%</t>
+  </si>
+  <si>
+    <t>BSE 100</t>
+  </si>
+  <si>
+    <t>24450.37</t>
+  </si>
+  <si>
+    <t>423.34</t>
+  </si>
+  <si>
+    <t>+1.76%</t>
+  </si>
+  <si>
+    <t>BSE SENSEX 50</t>
+  </si>
+  <si>
+    <t>24347.03</t>
+  </si>
+  <si>
+    <t>404.99</t>
+  </si>
+  <si>
+    <t>+1.69%</t>
+  </si>
+  <si>
+    <t>BSE SENSEX Next 50</t>
+  </si>
+  <si>
+    <t>78335.51</t>
+  </si>
+  <si>
+    <t>1582.74</t>
+  </si>
+  <si>
+    <t>+2.06%</t>
+  </si>
+  <si>
+    <t>BSE Bharat 22 Index</t>
+  </si>
+  <si>
+    <t>8941.57</t>
+  </si>
+  <si>
+    <t>142.61</t>
+  </si>
+  <si>
+    <t>+1.62%</t>
+  </si>
+  <si>
+    <t>BSE SENSEX SIXTY</t>
+  </si>
+  <si>
+    <t>31403.53</t>
+  </si>
+  <si>
+    <t>526.9</t>
+  </si>
+  <si>
+    <t>+1.71%</t>
+  </si>
+  <si>
+    <t>BSE 200</t>
+  </si>
+  <si>
+    <t>10619.10</t>
+  </si>
+  <si>
+    <t>191.85</t>
+  </si>
+  <si>
+    <t>+1.84%</t>
+  </si>
+  <si>
+    <t>BSE 150 MidCap Index</t>
+  </si>
+  <si>
+    <t>14975.17</t>
+  </si>
+  <si>
+    <t>342.15</t>
+  </si>
+  <si>
+    <t>+2.34%</t>
+  </si>
+  <si>
+    <t>BSE 250 SmallCap Index</t>
+  </si>
+  <si>
+    <t>5902.99</t>
+  </si>
+  <si>
+    <t>138.69</t>
+  </si>
+  <si>
+    <t>+2.41%</t>
+  </si>
+  <si>
+    <t>BSE 250 LargeMidCap Index</t>
+  </si>
+  <si>
+    <t>10070.67</t>
+  </si>
+  <si>
+    <t>185.71</t>
+  </si>
+  <si>
+    <t>+1.88%</t>
+  </si>
+  <si>
+    <t>BSE 400 MidSmallCap Index</t>
+  </si>
+  <si>
+    <t>10964.25</t>
+  </si>
+  <si>
+    <t>252.79</t>
+  </si>
+  <si>
+    <t>+2.36%</t>
+  </si>
+  <si>
+    <t>BSE 500</t>
+  </si>
+  <si>
+    <t>33645.89</t>
+  </si>
+  <si>
+    <t>636.32</t>
+  </si>
+  <si>
+    <t>+1.93%</t>
+  </si>
+  <si>
+    <t>BSE SmallCap Select Index</t>
+  </si>
+  <si>
+    <t>7231.99</t>
+  </si>
+  <si>
+    <t>214.35</t>
+  </si>
+  <si>
+    <t>+3.05%</t>
+  </si>
+  <si>
+    <t>BSE MidCap Select Index</t>
+  </si>
+  <si>
+    <t>15574.35</t>
+  </si>
+  <si>
+    <t>379.9</t>
+  </si>
+  <si>
+    <t>+2.50%</t>
+  </si>
+  <si>
+    <t>BSE 100 LargeCap TMC Index</t>
+  </si>
+  <si>
+    <t>8639.48</t>
+  </si>
+  <si>
+    <t>148.84</t>
+  </si>
+  <si>
+    <t>+1.75%</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>0.0 0%</t>
+  </si>
+  <si>
+    <t>BSE 1000</t>
+  </si>
+  <si>
+    <t>9971.85</t>
+  </si>
+  <si>
+    <t>189.21 +1.93%</t>
+  </si>
+  <si>
+    <t>38033.79</t>
+  </si>
+  <si>
+    <t>746.56 +2.00%</t>
+  </si>
+  <si>
+    <t>17528.12</t>
+  </si>
+  <si>
+    <t>311.71 +1.81%</t>
+  </si>
+  <si>
+    <t>389.60</t>
+  </si>
+  <si>
+    <t>6.72 +1.76%</t>
+  </si>
+  <si>
+    <t>BSE Focused IT</t>
+  </si>
+  <si>
+    <t>34389.17</t>
+  </si>
+  <si>
+    <t>149.78 +0.44%</t>
+  </si>
+  <si>
+    <t>BSE Momentum Index</t>
+  </si>
+  <si>
+    <t>2012.28</t>
+  </si>
+  <si>
+    <t>50.87 +2.59%</t>
+  </si>
+  <si>
+    <t>1711.38</t>
+  </si>
+  <si>
+    <t>34.91 +2.08%</t>
+  </si>
+  <si>
+    <t>1729.56</t>
+  </si>
+  <si>
+    <t>31.41 +1.85%</t>
+  </si>
+  <si>
+    <t>BSE Enhanced Value Index</t>
+  </si>
+  <si>
+    <t>983.96</t>
+  </si>
+  <si>
+    <t>18.17 +1.88%</t>
+  </si>
+  <si>
+    <t>BSE SENSEX SIXTY 65:35</t>
+  </si>
+  <si>
+    <t>32159.38</t>
+  </si>
+  <si>
+    <t>555.1 +1.76%</t>
+  </si>
+  <si>
+    <t>988.18</t>
+  </si>
+  <si>
+    <t>13.51 +1.39%</t>
+  </si>
+  <si>
+    <t>14313.99</t>
+  </si>
+  <si>
+    <t>127.83 +0.90%</t>
+  </si>
+  <si>
+    <t>BSE SME IPO</t>
+  </si>
+  <si>
+    <t>77587.83</t>
+  </si>
+  <si>
+    <t>384.36 +0.50%</t>
+  </si>
+  <si>
+    <t>BSE DOLLEX 30</t>
+  </si>
+  <si>
+    <t>6576.77</t>
+  </si>
+  <si>
+    <t>97.78 +1.51%</t>
+  </si>
+  <si>
+    <t>2691.80</t>
+  </si>
+  <si>
+    <t>43.54 +1.64%</t>
+  </si>
+  <si>
+    <t>1881.49</t>
+  </si>
+  <si>
+    <t>31.85 +1.72%</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Index Name</t>
+  </si>
+  <si>
+    <t>Highest Gain</t>
+  </si>
+  <si>
+    <t>75168.54</t>
+  </si>
+  <si>
+    <t>1305.98</t>
+  </si>
+  <si>
+    <t>Highest Loss</t>
+  </si>
+  <si>
+    <t>BSE 200 EQUAL WEIGHT INDEX</t>
+  </si>
+  <si>
+    <t>12291.74</t>
+  </si>
+  <si>
+    <t>251.89</t>
+  </si>
+  <si>
+    <t>BSE SELECT IPO</t>
+  </si>
+  <si>
+    <t>4013.01</t>
+  </si>
+  <si>
+    <t>78.14</t>
+  </si>
+  <si>
+    <t>BSE SENSEX EQUAL WEIGHT</t>
+  </si>
+  <si>
+    <t>BSE 500 Quality 50</t>
+  </si>
+  <si>
+    <t>20266.74</t>
+  </si>
+  <si>
+    <t>342.77</t>
+  </si>
+  <si>
+    <t>BSE 500 Momentum 50</t>
+  </si>
+  <si>
+    <t>40464.13</t>
+  </si>
+  <si>
+    <t>927.55</t>
+  </si>
+  <si>
+    <t>BSE INDIA SECTOR LEADERS</t>
+  </si>
+  <si>
+    <t>13783.13</t>
+  </si>
+  <si>
+    <t>242.17</t>
+  </si>
+  <si>
+    <t>BSE SELECT BUSINESS GROUPS</t>
+  </si>
+  <si>
+    <t>4124.50</t>
+  </si>
+  <si>
+    <t>76.27</t>
+  </si>
+  <si>
+    <t>BSE Commodities</t>
+  </si>
+  <si>
+    <t>7655.13</t>
+  </si>
+  <si>
+    <t>205.13</t>
+  </si>
+  <si>
+    <t>BSE Consumer Discretionary</t>
+  </si>
+  <si>
+    <t>8591.01</t>
+  </si>
+  <si>
+    <t>193.66</t>
+  </si>
+  <si>
+    <t>BSE Energy</t>
+  </si>
+  <si>
+    <t>11272.82</t>
+  </si>
+  <si>
+    <t>71.28</t>
+  </si>
+  <si>
+    <t>BSE Fast Moving Consumer Goods</t>
+  </si>
+  <si>
+    <t>17421.27</t>
+  </si>
+  <si>
+    <t>337.98</t>
   </si>
 </sst>
 </file>
@@ -31,7 +546,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="20">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -39,16 +554,138 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="14.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="8"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -56,12 +693,87 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFill="true" applyBorder="true" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -4969,4 +5681,2235 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="16.65625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.89453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.32421875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.1640625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="4.40234375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="8.828125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="10.40234375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="8.4453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="15.83984375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.90234375"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="1">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s" s="1">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s" s="1">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D75"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="23.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="8.40234375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.40234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="8.828125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="3">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="5">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D61" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D63" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D65" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D66" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D67" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D69" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D70" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D71" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D72" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D73" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D74" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D75" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="23.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="8.40234375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.71484375"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="7">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="8">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.5703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="5.48046875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.06640625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="10">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="11">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="12">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.72265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.5625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.40234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="7.40234375"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="13">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s" s="14">
+        <v>137</v>
+      </c>
+      <c r="C1" t="s" s="15">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s" s="16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="26.94140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="8.40234375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.40234375"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="17">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="18">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>